--- a/outputs/Block2_National_Final_Selection_v12.xlsx
+++ b/outputs/Block2_National_Final_Selection_v12.xlsx
@@ -519,7 +519,7 @@
         <v>0.5680217180041788</v>
       </c>
       <c r="G2">
-        <v>0.4319782819958212</v>
+        <v>0.4319782819958211</v>
       </c>
       <c r="H2" t="s">
         <v>20</v>
